--- a/server/templates/invoice-template.xlsx
+++ b/server/templates/invoice-template.xlsx
@@ -1935,7 +1935,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8">
       <c r="A8" s="56" t="n"/>
       <c r="B8" s="68" t="n"/>
       <c r="C8" s="68" t="n"/>
@@ -1986,7 +1986,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10">
       <c r="A10" s="56" t="n"/>
       <c r="D10" s="47" t="n"/>
       <c r="E10" s="47" t="n"/>
